--- a/Windows_Ransomware_Intrusion/evidence/FileSystem/metadata/Finance 20260424080823.xlsx
+++ b/Windows_Ransomware_Intrusion/evidence/FileSystem/metadata/Finance 20260424080823.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emma\Desktop\evidence\FileSystem\metadata\Parsed Metadata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emma/DFIR-Simulation-Platform/Windows_Ransomware_Intrusion/evidence/FileSystem/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F1BD5A3-2FC4-4E25-937A-CB5DF1F449DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EDBE3DE-A893-294E-A760-EBCF3886DBE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8508" yWindow="0" windowWidth="14628" windowHeight="12336" xr2:uid="{19E7828B-23A4-47C3-89D8-B5D9E63E5B4D}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="23120" windowHeight="11400" xr2:uid="{19E7828B-23A4-47C3-89D8-B5D9E63E5B4D}"/>
   </bookViews>
   <sheets>
     <sheet name="Finance 20260424080823" sheetId="1" r:id="rId1"/>
@@ -621,6 +621,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9258598C-7724-7844-B3B6-E58AC729E0C7}" name="Table1" displayName="Table1" ref="A1:H4" totalsRowShown="0">
+  <autoFilter ref="A1:H4" xr:uid="{9258598C-7724-7844-B3B6-E58AC729E0C7}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{1A78F922-CBFD-714F-B86D-D3E282BD2F87}" name="Name"/>
+    <tableColumn id="2" xr3:uid="{D837BECC-EEAB-5C40-A283-A2A840A17072}" name="Modified Time"/>
+    <tableColumn id="3" xr3:uid="{144021B3-BB5C-3145-A4DE-9F724D3E1485}" name="Change Time"/>
+    <tableColumn id="4" xr3:uid="{75D2D1C1-F90E-D747-8770-E388AEA50A3D}" name="Access Time"/>
+    <tableColumn id="5" xr3:uid="{DF60BCB1-8E2D-294E-ADC8-C19CA3025E70}" name="Created Time"/>
+    <tableColumn id="6" xr3:uid="{4B6CCBAA-84E6-B94C-9D5E-90996E5FD317}" name="Size"/>
+    <tableColumn id="7" xr3:uid="{4C310CF3-F89C-4142-8B26-A51D0F94505A}" name="Location"/>
+    <tableColumn id="8" xr3:uid="{48DB7278-E6EC-8041-A119-67BBBC362C10}" name="Extension"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -941,16 +958,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C8CCEF7-C34A-49AE-A902-F880D7A7B5BE}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="60.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -976,7 +993,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1002,7 +1019,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1028,7 +1045,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1056,5 +1073,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>